--- a/MaterialEstudiarCompetencias/Test 16 PF (plantilla puntajes).xlsx
+++ b/MaterialEstudiarCompetencias/Test 16 PF (plantilla puntajes).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kharlie\Desktop\TEST\Test 16 Factores de Personalidad (16-PF)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ceav300725\Downloads\073 - Test 16 Factores de Personalidad (16-PF)\Test 16 Factores de Personalidad (16-PF)\Test 16 PF (calificar)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34185418-DF59-4808-B29D-21E45045766B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF20D1E0-4F3C-4A3D-9F64-99F96579D840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1440" windowWidth="21600" windowHeight="11505"/>
+    <workbookView xWindow="-45" yWindow="1065" windowWidth="17610" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respuestas" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,13 @@
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="22">
   <si>
     <t>A</t>
   </si>
@@ -118,7 +123,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -505,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -548,7 +553,6 @@
       <protection locked="0" hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
@@ -571,29 +575,73 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -612,64 +660,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -690,9 +694,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -730,7 +734,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -836,7 +840,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -978,21 +982,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:GF197"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="17" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="2" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="2" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="2" hidden="1" customWidth="1"/>
     <col min="11" max="100" width="3" hidden="1" customWidth="1"/>
     <col min="101" max="188" width="4" hidden="1" customWidth="1"/>
@@ -1024,7 +1028,9 @@
       <c r="B3" s="12">
         <v>1</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
       <c r="W3" t="s">
@@ -1036,7 +1042,9 @@
       <c r="B4" s="13">
         <v>2</v>
       </c>
-      <c r="C4" s="15"/>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="W4" t="s">
@@ -1048,7 +1056,9 @@
       <c r="B5" s="13">
         <v>3</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
       <c r="W5" t="s">
@@ -1060,7 +1070,9 @@
       <c r="B6" s="13">
         <v>4</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
     </row>
@@ -1069,7 +1081,9 @@
       <c r="B7" s="13">
         <v>5</v>
       </c>
-      <c r="C7" s="15"/>
+      <c r="C7" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
     </row>
@@ -1078,7 +1092,9 @@
       <c r="B8" s="13">
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
     </row>
@@ -1087,7 +1103,9 @@
       <c r="B9" s="13">
         <v>7</v>
       </c>
-      <c r="C9" s="15"/>
+      <c r="C9" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
     </row>
@@ -1096,7 +1114,9 @@
       <c r="B10" s="13">
         <v>8</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
     </row>
@@ -1105,7 +1125,9 @@
       <c r="B11" s="13">
         <v>9</v>
       </c>
-      <c r="C11" s="15"/>
+      <c r="C11" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
     </row>
@@ -1114,7 +1136,9 @@
       <c r="B12" s="13">
         <v>10</v>
       </c>
-      <c r="C12" s="15"/>
+      <c r="C12" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
     </row>
@@ -1123,7 +1147,9 @@
       <c r="B13" s="13">
         <v>11</v>
       </c>
-      <c r="C13" s="15"/>
+      <c r="C13" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
     </row>
@@ -1132,7 +1158,9 @@
       <c r="B14" s="13">
         <v>12</v>
       </c>
-      <c r="C14" s="15"/>
+      <c r="C14" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
     </row>
@@ -1141,7 +1169,9 @@
       <c r="B15" s="13">
         <v>13</v>
       </c>
-      <c r="C15" s="15"/>
+      <c r="C15" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
     </row>
@@ -1150,7 +1180,9 @@
       <c r="B16" s="13">
         <v>14</v>
       </c>
-      <c r="C16" s="15"/>
+      <c r="C16" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
     </row>
@@ -1159,7 +1191,9 @@
       <c r="B17" s="13">
         <v>15</v>
       </c>
-      <c r="C17" s="15"/>
+      <c r="C17" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
     </row>
@@ -1168,7 +1202,9 @@
       <c r="B18" s="13">
         <v>16</v>
       </c>
-      <c r="C18" s="15"/>
+      <c r="C18" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
     </row>
@@ -1177,7 +1213,9 @@
       <c r="B19" s="13">
         <v>17</v>
       </c>
-      <c r="C19" s="15"/>
+      <c r="C19" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
     </row>
@@ -1186,7 +1224,9 @@
       <c r="B20" s="13">
         <v>18</v>
       </c>
-      <c r="C20" s="15"/>
+      <c r="C20" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
     </row>
@@ -1195,7 +1235,9 @@
       <c r="B21" s="13">
         <v>19</v>
       </c>
-      <c r="C21" s="15"/>
+      <c r="C21" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
     </row>
@@ -1204,7 +1246,9 @@
       <c r="B22" s="13">
         <v>20</v>
       </c>
-      <c r="C22" s="15"/>
+      <c r="C22" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
     </row>
@@ -1213,7 +1257,9 @@
       <c r="B23" s="13">
         <v>21</v>
       </c>
-      <c r="C23" s="15"/>
+      <c r="C23" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
     </row>
@@ -1222,7 +1268,9 @@
       <c r="B24" s="13">
         <v>22</v>
       </c>
-      <c r="C24" s="15"/>
+      <c r="C24" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
     </row>
@@ -1231,7 +1279,9 @@
       <c r="B25" s="13">
         <v>23</v>
       </c>
-      <c r="C25" s="15"/>
+      <c r="C25" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
     </row>
@@ -1240,7 +1290,9 @@
       <c r="B26" s="13">
         <v>24</v>
       </c>
-      <c r="C26" s="15"/>
+      <c r="C26" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
     </row>
@@ -1249,7 +1301,9 @@
       <c r="B27" s="13">
         <v>25</v>
       </c>
-      <c r="C27" s="15"/>
+      <c r="C27" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
     </row>
@@ -1258,7 +1312,9 @@
       <c r="B28" s="13">
         <v>26</v>
       </c>
-      <c r="C28" s="15"/>
+      <c r="C28" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
     </row>
@@ -1267,7 +1323,9 @@
       <c r="B29" s="13">
         <v>27</v>
       </c>
-      <c r="C29" s="15"/>
+      <c r="C29" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16"/>
     </row>
@@ -1276,7 +1334,9 @@
       <c r="B30" s="13">
         <v>28</v>
       </c>
-      <c r="C30" s="15"/>
+      <c r="C30" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
     </row>
@@ -1285,7 +1345,9 @@
       <c r="B31" s="13">
         <v>29</v>
       </c>
-      <c r="C31" s="15"/>
+      <c r="C31" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
     </row>
@@ -1294,7 +1356,9 @@
       <c r="B32" s="13">
         <v>30</v>
       </c>
-      <c r="C32" s="15"/>
+      <c r="C32" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
     </row>
@@ -1303,7 +1367,9 @@
       <c r="B33" s="13">
         <v>31</v>
       </c>
-      <c r="C33" s="15"/>
+      <c r="C33" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
     </row>
@@ -1312,7 +1378,9 @@
       <c r="B34" s="13">
         <v>32</v>
       </c>
-      <c r="C34" s="15"/>
+      <c r="C34" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
     </row>
@@ -1321,7 +1389,9 @@
       <c r="B35" s="13">
         <v>33</v>
       </c>
-      <c r="C35" s="15"/>
+      <c r="C35" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
     </row>
@@ -1330,7 +1400,9 @@
       <c r="B36" s="13">
         <v>34</v>
       </c>
-      <c r="C36" s="15"/>
+      <c r="C36" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
     </row>
@@ -1339,7 +1411,9 @@
       <c r="B37" s="13">
         <v>35</v>
       </c>
-      <c r="C37" s="15"/>
+      <c r="C37" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
     </row>
@@ -1348,7 +1422,9 @@
       <c r="B38" s="13">
         <v>36</v>
       </c>
-      <c r="C38" s="15"/>
+      <c r="C38" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
     </row>
@@ -1357,7 +1433,9 @@
       <c r="B39" s="13">
         <v>37</v>
       </c>
-      <c r="C39" s="15"/>
+      <c r="C39" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
     </row>
@@ -1366,7 +1444,9 @@
       <c r="B40" s="13">
         <v>38</v>
       </c>
-      <c r="C40" s="15"/>
+      <c r="C40" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
     </row>
@@ -1375,7 +1455,9 @@
       <c r="B41" s="13">
         <v>39</v>
       </c>
-      <c r="C41" s="15"/>
+      <c r="C41" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
     </row>
@@ -1384,7 +1466,9 @@
       <c r="B42" s="13">
         <v>40</v>
       </c>
-      <c r="C42" s="15"/>
+      <c r="C42" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
@@ -1393,7 +1477,9 @@
       <c r="B43" s="13">
         <v>41</v>
       </c>
-      <c r="C43" s="15"/>
+      <c r="C43" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
@@ -1402,7 +1488,9 @@
       <c r="B44" s="13">
         <v>42</v>
       </c>
-      <c r="C44" s="15"/>
+      <c r="C44" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
     </row>
@@ -1411,7 +1499,9 @@
       <c r="B45" s="13">
         <v>43</v>
       </c>
-      <c r="C45" s="15"/>
+      <c r="C45" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
@@ -1420,7 +1510,9 @@
       <c r="B46" s="13">
         <v>44</v>
       </c>
-      <c r="C46" s="15"/>
+      <c r="C46" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
     </row>
@@ -1429,7 +1521,9 @@
       <c r="B47" s="13">
         <v>45</v>
       </c>
-      <c r="C47" s="15"/>
+      <c r="C47" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
@@ -1438,7 +1532,9 @@
       <c r="B48" s="13">
         <v>46</v>
       </c>
-      <c r="C48" s="15"/>
+      <c r="C48" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
     </row>
@@ -1447,7 +1543,9 @@
       <c r="B49" s="13">
         <v>47</v>
       </c>
-      <c r="C49" s="15"/>
+      <c r="C49" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
     </row>
@@ -1456,7 +1554,9 @@
       <c r="B50" s="13">
         <v>48</v>
       </c>
-      <c r="C50" s="15"/>
+      <c r="C50" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
     </row>
@@ -1465,7 +1565,9 @@
       <c r="B51" s="13">
         <v>49</v>
       </c>
-      <c r="C51" s="15"/>
+      <c r="C51" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
     </row>
@@ -1474,7 +1576,9 @@
       <c r="B52" s="13">
         <v>50</v>
       </c>
-      <c r="C52" s="15"/>
+      <c r="C52" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
     </row>
@@ -1483,7 +1587,9 @@
       <c r="B53" s="13">
         <v>51</v>
       </c>
-      <c r="C53" s="15"/>
+      <c r="C53" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
     </row>
@@ -1492,7 +1598,9 @@
       <c r="B54" s="13">
         <v>52</v>
       </c>
-      <c r="C54" s="15"/>
+      <c r="C54" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
     </row>
@@ -1501,7 +1609,9 @@
       <c r="B55" s="13">
         <v>53</v>
       </c>
-      <c r="C55" s="15"/>
+      <c r="C55" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
     </row>
@@ -1510,7 +1620,9 @@
       <c r="B56" s="13">
         <v>54</v>
       </c>
-      <c r="C56" s="15"/>
+      <c r="C56" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
     </row>
@@ -1519,7 +1631,9 @@
       <c r="B57" s="13">
         <v>55</v>
       </c>
-      <c r="C57" s="15"/>
+      <c r="C57" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
     </row>
@@ -1528,7 +1642,9 @@
       <c r="B58" s="13">
         <v>56</v>
       </c>
-      <c r="C58" s="15"/>
+      <c r="C58" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
     </row>
@@ -1537,7 +1653,9 @@
       <c r="B59" s="13">
         <v>57</v>
       </c>
-      <c r="C59" s="15"/>
+      <c r="C59" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
     </row>
@@ -1546,7 +1664,9 @@
       <c r="B60" s="13">
         <v>58</v>
       </c>
-      <c r="C60" s="15"/>
+      <c r="C60" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
     </row>
@@ -1555,7 +1675,9 @@
       <c r="B61" s="13">
         <v>59</v>
       </c>
-      <c r="C61" s="15"/>
+      <c r="C61" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
     </row>
@@ -1564,7 +1686,9 @@
       <c r="B62" s="13">
         <v>60</v>
       </c>
-      <c r="C62" s="15"/>
+      <c r="C62" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D62" s="16"/>
       <c r="E62" s="16"/>
     </row>
@@ -1573,7 +1697,9 @@
       <c r="B63" s="13">
         <v>61</v>
       </c>
-      <c r="C63" s="15"/>
+      <c r="C63" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
     </row>
@@ -1582,7 +1708,9 @@
       <c r="B64" s="13">
         <v>62</v>
       </c>
-      <c r="C64" s="15"/>
+      <c r="C64" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D64" s="16"/>
       <c r="E64" s="16"/>
     </row>
@@ -1591,7 +1719,9 @@
       <c r="B65" s="13">
         <v>63</v>
       </c>
-      <c r="C65" s="15"/>
+      <c r="C65" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D65" s="16"/>
       <c r="E65" s="16"/>
     </row>
@@ -1600,7 +1730,9 @@
       <c r="B66" s="13">
         <v>64</v>
       </c>
-      <c r="C66" s="15"/>
+      <c r="C66" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D66" s="16"/>
       <c r="E66" s="16"/>
     </row>
@@ -1609,7 +1741,9 @@
       <c r="B67" s="13">
         <v>65</v>
       </c>
-      <c r="C67" s="15"/>
+      <c r="C67" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D67" s="16"/>
       <c r="E67" s="16"/>
     </row>
@@ -1618,7 +1752,9 @@
       <c r="B68" s="13">
         <v>66</v>
       </c>
-      <c r="C68" s="15"/>
+      <c r="C68" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D68" s="16"/>
       <c r="E68" s="16"/>
     </row>
@@ -1627,7 +1763,9 @@
       <c r="B69" s="13">
         <v>67</v>
       </c>
-      <c r="C69" s="15"/>
+      <c r="C69" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
     </row>
@@ -1636,7 +1774,9 @@
       <c r="B70" s="13">
         <v>68</v>
       </c>
-      <c r="C70" s="15"/>
+      <c r="C70" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D70" s="16"/>
       <c r="E70" s="16"/>
     </row>
@@ -1645,7 +1785,9 @@
       <c r="B71" s="13">
         <v>69</v>
       </c>
-      <c r="C71" s="15"/>
+      <c r="C71" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D71" s="16"/>
       <c r="E71" s="16"/>
     </row>
@@ -1654,7 +1796,9 @@
       <c r="B72" s="13">
         <v>70</v>
       </c>
-      <c r="C72" s="15"/>
+      <c r="C72" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D72" s="16"/>
       <c r="E72" s="16"/>
     </row>
@@ -1663,7 +1807,9 @@
       <c r="B73" s="13">
         <v>71</v>
       </c>
-      <c r="C73" s="15"/>
+      <c r="C73" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D73" s="16"/>
       <c r="E73" s="16"/>
     </row>
@@ -1672,7 +1818,9 @@
       <c r="B74" s="13">
         <v>72</v>
       </c>
-      <c r="C74" s="15"/>
+      <c r="C74" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D74" s="16"/>
       <c r="E74" s="16"/>
     </row>
@@ -1681,7 +1829,9 @@
       <c r="B75" s="13">
         <v>73</v>
       </c>
-      <c r="C75" s="15"/>
+      <c r="C75" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D75" s="16"/>
       <c r="E75" s="16"/>
     </row>
@@ -1690,7 +1840,9 @@
       <c r="B76" s="13">
         <v>74</v>
       </c>
-      <c r="C76" s="15"/>
+      <c r="C76" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D76" s="16"/>
       <c r="E76" s="16"/>
     </row>
@@ -1699,7 +1851,9 @@
       <c r="B77" s="13">
         <v>75</v>
       </c>
-      <c r="C77" s="15"/>
+      <c r="C77" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D77" s="16"/>
       <c r="E77" s="16"/>
     </row>
@@ -1708,7 +1862,9 @@
       <c r="B78" s="13">
         <v>76</v>
       </c>
-      <c r="C78" s="15"/>
+      <c r="C78" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D78" s="16"/>
       <c r="E78" s="16"/>
     </row>
@@ -1717,7 +1873,9 @@
       <c r="B79" s="13">
         <v>77</v>
       </c>
-      <c r="C79" s="15"/>
+      <c r="C79" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D79" s="16"/>
       <c r="E79" s="16"/>
     </row>
@@ -1726,7 +1884,9 @@
       <c r="B80" s="13">
         <v>78</v>
       </c>
-      <c r="C80" s="15"/>
+      <c r="C80" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
     </row>
@@ -1735,7 +1895,9 @@
       <c r="B81" s="13">
         <v>79</v>
       </c>
-      <c r="C81" s="15"/>
+      <c r="C81" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D81" s="16"/>
       <c r="E81" s="16"/>
     </row>
@@ -1744,7 +1906,9 @@
       <c r="B82" s="13">
         <v>80</v>
       </c>
-      <c r="C82" s="15"/>
+      <c r="C82" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D82" s="16"/>
       <c r="E82" s="16"/>
     </row>
@@ -1753,7 +1917,9 @@
       <c r="B83" s="13">
         <v>81</v>
       </c>
-      <c r="C83" s="15"/>
+      <c r="C83" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D83" s="16"/>
       <c r="E83" s="16"/>
     </row>
@@ -1762,7 +1928,9 @@
       <c r="B84" s="13">
         <v>82</v>
       </c>
-      <c r="C84" s="15"/>
+      <c r="C84" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D84" s="16"/>
       <c r="E84" s="16"/>
     </row>
@@ -1771,7 +1939,9 @@
       <c r="B85" s="13">
         <v>83</v>
       </c>
-      <c r="C85" s="15"/>
+      <c r="C85" s="15" t="s">
+        <v>1</v>
+      </c>
       <c r="D85" s="16"/>
       <c r="E85" s="16"/>
     </row>
@@ -1780,7 +1950,9 @@
       <c r="B86" s="13">
         <v>84</v>
       </c>
-      <c r="C86" s="15"/>
+      <c r="C86" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
     </row>
@@ -1789,7 +1961,9 @@
       <c r="B87" s="13">
         <v>85</v>
       </c>
-      <c r="C87" s="15"/>
+      <c r="C87" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D87" s="16"/>
       <c r="E87" s="16"/>
     </row>
@@ -1798,7 +1972,9 @@
       <c r="B88" s="13">
         <v>86</v>
       </c>
-      <c r="C88" s="15"/>
+      <c r="C88" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D88" s="16"/>
       <c r="E88" s="16"/>
     </row>
@@ -1807,7 +1983,9 @@
       <c r="B89" s="13">
         <v>87</v>
       </c>
-      <c r="C89" s="15"/>
+      <c r="C89" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D89" s="16"/>
       <c r="E89" s="16"/>
     </row>
@@ -1816,7 +1994,9 @@
       <c r="B90" s="13">
         <v>88</v>
       </c>
-      <c r="C90" s="15"/>
+      <c r="C90" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="D90" s="16"/>
       <c r="E90" s="16"/>
     </row>
@@ -1825,7 +2005,9 @@
       <c r="B91" s="13">
         <v>89</v>
       </c>
-      <c r="C91" s="15"/>
+      <c r="C91" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D91" s="16"/>
       <c r="E91" s="16"/>
     </row>
@@ -1834,7 +2016,9 @@
       <c r="B92" s="13">
         <v>90</v>
       </c>
-      <c r="C92" s="15"/>
+      <c r="C92" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D92" s="16"/>
       <c r="E92" s="16"/>
     </row>
@@ -1843,7 +2027,9 @@
       <c r="B93" s="13">
         <v>91</v>
       </c>
-      <c r="C93" s="15"/>
+      <c r="C93" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D93" s="16"/>
       <c r="E93" s="16"/>
     </row>
@@ -1852,7 +2038,9 @@
       <c r="B94" s="13">
         <v>92</v>
       </c>
-      <c r="C94" s="15"/>
+      <c r="C94" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D94" s="16"/>
       <c r="E94" s="16"/>
     </row>
@@ -1861,7 +2049,9 @@
       <c r="B95" s="13">
         <v>93</v>
       </c>
-      <c r="C95" s="15"/>
+      <c r="C95" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D95" s="16"/>
       <c r="E95" s="16"/>
     </row>
@@ -1870,7 +2060,9 @@
       <c r="B96" s="13">
         <v>94</v>
       </c>
-      <c r="C96" s="15"/>
+      <c r="C96" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D96" s="16"/>
       <c r="E96" s="16"/>
     </row>
@@ -1879,7 +2071,9 @@
       <c r="B97" s="13">
         <v>95</v>
       </c>
-      <c r="C97" s="15"/>
+      <c r="C97" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D97" s="16"/>
       <c r="E97" s="16"/>
     </row>
@@ -1888,7 +2082,9 @@
       <c r="B98" s="13">
         <v>96</v>
       </c>
-      <c r="C98" s="15"/>
+      <c r="C98" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D98" s="16"/>
       <c r="E98" s="16"/>
     </row>
@@ -1897,7 +2093,9 @@
       <c r="B99" s="13">
         <v>97</v>
       </c>
-      <c r="C99" s="15"/>
+      <c r="C99" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D99" s="16"/>
       <c r="E99" s="16"/>
     </row>
@@ -1906,7 +2104,9 @@
       <c r="B100" s="13">
         <v>98</v>
       </c>
-      <c r="C100" s="15"/>
+      <c r="C100" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D100" s="16"/>
       <c r="E100" s="16"/>
     </row>
@@ -1915,7 +2115,9 @@
       <c r="B101" s="13">
         <v>99</v>
       </c>
-      <c r="C101" s="15"/>
+      <c r="C101" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D101" s="16"/>
       <c r="E101" s="16"/>
     </row>
@@ -1924,7 +2126,9 @@
       <c r="B102" s="13">
         <v>100</v>
       </c>
-      <c r="C102" s="15"/>
+      <c r="C102" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D102" s="16"/>
       <c r="E102" s="16"/>
     </row>
@@ -1933,7 +2137,9 @@
       <c r="B103" s="13">
         <v>101</v>
       </c>
-      <c r="C103" s="15"/>
+      <c r="C103" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D103" s="16"/>
       <c r="E103" s="16"/>
     </row>
@@ -1942,7 +2148,9 @@
       <c r="B104" s="13">
         <v>102</v>
       </c>
-      <c r="C104" s="15"/>
+      <c r="C104" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D104" s="16"/>
       <c r="E104" s="16"/>
     </row>
@@ -1951,7 +2159,9 @@
       <c r="B105" s="13">
         <v>103</v>
       </c>
-      <c r="C105" s="15"/>
+      <c r="C105" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D105" s="16"/>
       <c r="E105" s="16"/>
     </row>
@@ -1960,7 +2170,9 @@
       <c r="B106" s="13">
         <v>104</v>
       </c>
-      <c r="C106" s="15"/>
+      <c r="C106" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D106" s="16"/>
       <c r="E106" s="16"/>
     </row>
@@ -1969,7 +2181,9 @@
       <c r="B107" s="13">
         <v>105</v>
       </c>
-      <c r="C107" s="15"/>
+      <c r="C107" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D107" s="16"/>
       <c r="E107" s="16"/>
     </row>
@@ -1978,7 +2192,9 @@
       <c r="B108" s="13">
         <v>106</v>
       </c>
-      <c r="C108" s="15"/>
+      <c r="C108" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D108" s="16"/>
       <c r="E108" s="16"/>
     </row>
@@ -1987,7 +2203,9 @@
       <c r="B109" s="13">
         <v>107</v>
       </c>
-      <c r="C109" s="15"/>
+      <c r="C109" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D109" s="16"/>
       <c r="E109" s="16"/>
     </row>
@@ -1996,7 +2214,9 @@
       <c r="B110" s="13">
         <v>108</v>
       </c>
-      <c r="C110" s="15"/>
+      <c r="C110" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D110" s="16"/>
       <c r="E110" s="16"/>
     </row>
@@ -2005,7 +2225,9 @@
       <c r="B111" s="13">
         <v>109</v>
       </c>
-      <c r="C111" s="15"/>
+      <c r="C111" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D111" s="16"/>
       <c r="E111" s="16"/>
     </row>
@@ -2014,7 +2236,9 @@
       <c r="B112" s="13">
         <v>110</v>
       </c>
-      <c r="C112" s="15"/>
+      <c r="C112" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D112" s="16"/>
       <c r="E112" s="16"/>
     </row>
@@ -2023,7 +2247,9 @@
       <c r="B113" s="13">
         <v>111</v>
       </c>
-      <c r="C113" s="15"/>
+      <c r="C113" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D113" s="16"/>
       <c r="E113" s="16"/>
     </row>
@@ -2032,7 +2258,9 @@
       <c r="B114" s="13">
         <v>112</v>
       </c>
-      <c r="C114" s="15"/>
+      <c r="C114" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D114" s="16"/>
       <c r="E114" s="16"/>
     </row>
@@ -2041,7 +2269,9 @@
       <c r="B115" s="13">
         <v>113</v>
       </c>
-      <c r="C115" s="15"/>
+      <c r="C115" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
     </row>
@@ -2050,7 +2280,9 @@
       <c r="B116" s="13">
         <v>114</v>
       </c>
-      <c r="C116" s="15"/>
+      <c r="C116" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D116" s="16"/>
       <c r="E116" s="16"/>
     </row>
@@ -2059,7 +2291,9 @@
       <c r="B117" s="13">
         <v>115</v>
       </c>
-      <c r="C117" s="15"/>
+      <c r="C117" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D117" s="16"/>
       <c r="E117" s="16"/>
     </row>
@@ -2068,7 +2302,9 @@
       <c r="B118" s="13">
         <v>116</v>
       </c>
-      <c r="C118" s="15"/>
+      <c r="C118" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D118" s="16"/>
       <c r="E118" s="16"/>
     </row>
@@ -2077,7 +2313,9 @@
       <c r="B119" s="13">
         <v>117</v>
       </c>
-      <c r="C119" s="15"/>
+      <c r="C119" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D119" s="16"/>
       <c r="E119" s="16"/>
     </row>
@@ -2086,7 +2324,9 @@
       <c r="B120" s="13">
         <v>118</v>
       </c>
-      <c r="C120" s="15"/>
+      <c r="C120" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D120" s="16"/>
       <c r="E120" s="16"/>
     </row>
@@ -2095,7 +2335,9 @@
       <c r="B121" s="13">
         <v>119</v>
       </c>
-      <c r="C121" s="15"/>
+      <c r="C121" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D121" s="16"/>
       <c r="E121" s="16"/>
     </row>
@@ -2104,7 +2346,9 @@
       <c r="B122" s="13">
         <v>120</v>
       </c>
-      <c r="C122" s="15"/>
+      <c r="C122" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D122" s="16"/>
       <c r="E122" s="16"/>
     </row>
@@ -2113,7 +2357,9 @@
       <c r="B123" s="13">
         <v>121</v>
       </c>
-      <c r="C123" s="15"/>
+      <c r="C123" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D123" s="16"/>
       <c r="E123" s="16"/>
     </row>
@@ -2122,7 +2368,9 @@
       <c r="B124" s="13">
         <v>122</v>
       </c>
-      <c r="C124" s="15"/>
+      <c r="C124" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D124" s="16"/>
       <c r="E124" s="16"/>
     </row>
@@ -2131,7 +2379,9 @@
       <c r="B125" s="13">
         <v>123</v>
       </c>
-      <c r="C125" s="15"/>
+      <c r="C125" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D125" s="16"/>
       <c r="E125" s="16"/>
     </row>
@@ -2140,7 +2390,9 @@
       <c r="B126" s="13">
         <v>124</v>
       </c>
-      <c r="C126" s="15"/>
+      <c r="C126" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D126" s="16"/>
       <c r="E126" s="16"/>
     </row>
@@ -2149,7 +2401,9 @@
       <c r="B127" s="13">
         <v>125</v>
       </c>
-      <c r="C127" s="15"/>
+      <c r="C127" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D127" s="16"/>
       <c r="E127" s="16"/>
     </row>
@@ -2158,7 +2412,9 @@
       <c r="B128" s="13">
         <v>126</v>
       </c>
-      <c r="C128" s="15"/>
+      <c r="C128" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D128" s="16"/>
       <c r="E128" s="16"/>
     </row>
@@ -2167,7 +2423,9 @@
       <c r="B129" s="13">
         <v>127</v>
       </c>
-      <c r="C129" s="15"/>
+      <c r="C129" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D129" s="16"/>
       <c r="E129" s="16"/>
     </row>
@@ -2176,7 +2434,9 @@
       <c r="B130" s="13">
         <v>128</v>
       </c>
-      <c r="C130" s="15"/>
+      <c r="C130" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D130" s="16"/>
       <c r="E130" s="16"/>
     </row>
@@ -2185,7 +2445,9 @@
       <c r="B131" s="13">
         <v>129</v>
       </c>
-      <c r="C131" s="15"/>
+      <c r="C131" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D131" s="16"/>
       <c r="E131" s="16"/>
     </row>
@@ -2194,7 +2456,9 @@
       <c r="B132" s="13">
         <v>130</v>
       </c>
-      <c r="C132" s="15"/>
+      <c r="C132" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D132" s="16"/>
       <c r="E132" s="16"/>
     </row>
@@ -2203,7 +2467,9 @@
       <c r="B133" s="13">
         <v>131</v>
       </c>
-      <c r="C133" s="15"/>
+      <c r="C133" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D133" s="16"/>
       <c r="E133" s="16"/>
     </row>
@@ -2212,7 +2478,9 @@
       <c r="B134" s="13">
         <v>132</v>
       </c>
-      <c r="C134" s="15"/>
+      <c r="C134" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D134" s="16"/>
       <c r="E134" s="16"/>
     </row>
@@ -2221,7 +2489,9 @@
       <c r="B135" s="13">
         <v>133</v>
       </c>
-      <c r="C135" s="15"/>
+      <c r="C135" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D135" s="16"/>
       <c r="E135" s="16"/>
     </row>
@@ -2230,7 +2500,9 @@
       <c r="B136" s="13">
         <v>134</v>
       </c>
-      <c r="C136" s="15"/>
+      <c r="C136" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D136" s="16"/>
       <c r="E136" s="16"/>
     </row>
@@ -2239,7 +2511,9 @@
       <c r="B137" s="13">
         <v>135</v>
       </c>
-      <c r="C137" s="15"/>
+      <c r="C137" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D137" s="16"/>
       <c r="E137" s="16"/>
     </row>
@@ -2248,7 +2522,9 @@
       <c r="B138" s="13">
         <v>136</v>
       </c>
-      <c r="C138" s="15"/>
+      <c r="C138" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D138" s="16"/>
       <c r="E138" s="16"/>
     </row>
@@ -2257,7 +2533,9 @@
       <c r="B139" s="13">
         <v>137</v>
       </c>
-      <c r="C139" s="15"/>
+      <c r="C139" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D139" s="16"/>
       <c r="E139" s="16"/>
     </row>
@@ -2266,7 +2544,9 @@
       <c r="B140" s="13">
         <v>138</v>
       </c>
-      <c r="C140" s="15"/>
+      <c r="C140" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D140" s="16"/>
       <c r="E140" s="16"/>
     </row>
@@ -2275,7 +2555,9 @@
       <c r="B141" s="13">
         <v>139</v>
       </c>
-      <c r="C141" s="15"/>
+      <c r="C141" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D141" s="16"/>
       <c r="E141" s="16"/>
     </row>
@@ -2284,7 +2566,9 @@
       <c r="B142" s="13">
         <v>140</v>
       </c>
-      <c r="C142" s="15"/>
+      <c r="C142" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D142" s="16"/>
       <c r="E142" s="16"/>
     </row>
@@ -2293,7 +2577,9 @@
       <c r="B143" s="13">
         <v>141</v>
       </c>
-      <c r="C143" s="15"/>
+      <c r="C143" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D143" s="16"/>
       <c r="E143" s="16"/>
     </row>
@@ -2302,7 +2588,9 @@
       <c r="B144" s="13">
         <v>142</v>
       </c>
-      <c r="C144" s="15"/>
+      <c r="C144" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D144" s="16"/>
       <c r="E144" s="16"/>
     </row>
@@ -2311,7 +2599,9 @@
       <c r="B145" s="13">
         <v>143</v>
       </c>
-      <c r="C145" s="15"/>
+      <c r="C145" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D145" s="16"/>
       <c r="E145" s="16"/>
     </row>
@@ -2320,7 +2610,9 @@
       <c r="B146" s="13">
         <v>144</v>
       </c>
-      <c r="C146" s="15"/>
+      <c r="C146" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D146" s="16"/>
       <c r="E146" s="16"/>
     </row>
@@ -2329,7 +2621,9 @@
       <c r="B147" s="13">
         <v>145</v>
       </c>
-      <c r="C147" s="15"/>
+      <c r="C147" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D147" s="16"/>
       <c r="E147" s="16"/>
     </row>
@@ -2338,7 +2632,9 @@
       <c r="B148" s="13">
         <v>146</v>
       </c>
-      <c r="C148" s="15"/>
+      <c r="C148" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D148" s="16"/>
       <c r="E148" s="16"/>
     </row>
@@ -2347,7 +2643,9 @@
       <c r="B149" s="13">
         <v>147</v>
       </c>
-      <c r="C149" s="15"/>
+      <c r="C149" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D149" s="16"/>
       <c r="E149" s="16"/>
     </row>
@@ -2356,7 +2654,9 @@
       <c r="B150" s="13">
         <v>148</v>
       </c>
-      <c r="C150" s="15"/>
+      <c r="C150" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D150" s="16"/>
       <c r="E150" s="16"/>
     </row>
@@ -2365,7 +2665,9 @@
       <c r="B151" s="13">
         <v>149</v>
       </c>
-      <c r="C151" s="15"/>
+      <c r="C151" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D151" s="16"/>
       <c r="E151" s="16"/>
     </row>
@@ -2374,7 +2676,9 @@
       <c r="B152" s="13">
         <v>150</v>
       </c>
-      <c r="C152" s="15"/>
+      <c r="C152" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D152" s="16"/>
       <c r="E152" s="16"/>
     </row>
@@ -2383,7 +2687,9 @@
       <c r="B153" s="13">
         <v>151</v>
       </c>
-      <c r="C153" s="15"/>
+      <c r="C153" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D153" s="16"/>
       <c r="E153" s="16"/>
     </row>
@@ -2392,7 +2698,9 @@
       <c r="B154" s="13">
         <v>152</v>
       </c>
-      <c r="C154" s="15"/>
+      <c r="C154" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D154" s="16"/>
       <c r="E154" s="16"/>
     </row>
@@ -2401,7 +2709,9 @@
       <c r="B155" s="13">
         <v>153</v>
       </c>
-      <c r="C155" s="15"/>
+      <c r="C155" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D155" s="16"/>
       <c r="E155" s="16"/>
     </row>
@@ -2410,7 +2720,9 @@
       <c r="B156" s="13">
         <v>154</v>
       </c>
-      <c r="C156" s="15"/>
+      <c r="C156" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D156" s="16"/>
       <c r="E156" s="16"/>
     </row>
@@ -2419,7 +2731,9 @@
       <c r="B157" s="13">
         <v>155</v>
       </c>
-      <c r="C157" s="15"/>
+      <c r="C157" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D157" s="16"/>
       <c r="E157" s="16"/>
     </row>
@@ -2428,7 +2742,9 @@
       <c r="B158" s="13">
         <v>156</v>
       </c>
-      <c r="C158" s="15"/>
+      <c r="C158" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D158" s="16"/>
       <c r="E158" s="16"/>
     </row>
@@ -2437,7 +2753,9 @@
       <c r="B159" s="13">
         <v>157</v>
       </c>
-      <c r="C159" s="15"/>
+      <c r="C159" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D159" s="16"/>
       <c r="E159" s="16"/>
     </row>
@@ -2446,7 +2764,9 @@
       <c r="B160" s="13">
         <v>158</v>
       </c>
-      <c r="C160" s="15"/>
+      <c r="C160" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D160" s="16"/>
       <c r="E160" s="16"/>
     </row>
@@ -2455,7 +2775,9 @@
       <c r="B161" s="13">
         <v>159</v>
       </c>
-      <c r="C161" s="15"/>
+      <c r="C161" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D161" s="16"/>
       <c r="E161" s="16"/>
     </row>
@@ -2464,7 +2786,9 @@
       <c r="B162" s="13">
         <v>160</v>
       </c>
-      <c r="C162" s="15"/>
+      <c r="C162" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D162" s="16"/>
       <c r="E162" s="16"/>
     </row>
@@ -2473,7 +2797,9 @@
       <c r="B163" s="13">
         <v>161</v>
       </c>
-      <c r="C163" s="15"/>
+      <c r="C163" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D163" s="16"/>
       <c r="E163" s="16"/>
     </row>
@@ -2482,7 +2808,9 @@
       <c r="B164" s="13">
         <v>162</v>
       </c>
-      <c r="C164" s="15"/>
+      <c r="C164" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D164" s="16"/>
       <c r="E164" s="16"/>
     </row>
@@ -2491,7 +2819,9 @@
       <c r="B165" s="13">
         <v>163</v>
       </c>
-      <c r="C165" s="15"/>
+      <c r="C165" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D165" s="16"/>
       <c r="E165" s="16"/>
     </row>
@@ -2500,7 +2830,9 @@
       <c r="B166" s="13">
         <v>164</v>
       </c>
-      <c r="C166" s="15"/>
+      <c r="C166" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D166" s="16"/>
       <c r="E166" s="16"/>
     </row>
@@ -2509,7 +2841,9 @@
       <c r="B167" s="13">
         <v>165</v>
       </c>
-      <c r="C167" s="15"/>
+      <c r="C167" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D167" s="16"/>
       <c r="E167" s="16"/>
     </row>
@@ -2518,7 +2852,9 @@
       <c r="B168" s="13">
         <v>166</v>
       </c>
-      <c r="C168" s="15"/>
+      <c r="C168" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D168" s="16"/>
       <c r="E168" s="16"/>
     </row>
@@ -2527,7 +2863,9 @@
       <c r="B169" s="13">
         <v>167</v>
       </c>
-      <c r="C169" s="15"/>
+      <c r="C169" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D169" s="16"/>
       <c r="E169" s="16"/>
     </row>
@@ -2536,7 +2874,9 @@
       <c r="B170" s="13">
         <v>168</v>
       </c>
-      <c r="C170" s="15"/>
+      <c r="C170" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D170" s="16"/>
       <c r="E170" s="16"/>
     </row>
@@ -2545,7 +2885,9 @@
       <c r="B171" s="13">
         <v>169</v>
       </c>
-      <c r="C171" s="15"/>
+      <c r="C171" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D171" s="16"/>
       <c r="E171" s="16"/>
     </row>
@@ -2554,7 +2896,9 @@
       <c r="B172" s="13">
         <v>170</v>
       </c>
-      <c r="C172" s="15"/>
+      <c r="C172" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D172" s="16"/>
       <c r="E172" s="16"/>
     </row>
@@ -2563,7 +2907,9 @@
       <c r="B173" s="13">
         <v>171</v>
       </c>
-      <c r="C173" s="15"/>
+      <c r="C173" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D173" s="16"/>
       <c r="E173" s="16"/>
     </row>
@@ -2572,7 +2918,9 @@
       <c r="B174" s="13">
         <v>172</v>
       </c>
-      <c r="C174" s="15"/>
+      <c r="C174" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D174" s="16"/>
       <c r="E174" s="16"/>
     </row>
@@ -2581,7 +2929,9 @@
       <c r="B175" s="13">
         <v>173</v>
       </c>
-      <c r="C175" s="15"/>
+      <c r="C175" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D175" s="16"/>
       <c r="E175" s="16"/>
     </row>
@@ -2590,7 +2940,9 @@
       <c r="B176" s="13">
         <v>174</v>
       </c>
-      <c r="C176" s="15"/>
+      <c r="C176" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D176" s="16"/>
       <c r="E176" s="16"/>
     </row>
@@ -2599,7 +2951,9 @@
       <c r="B177" s="13">
         <v>175</v>
       </c>
-      <c r="C177" s="15"/>
+      <c r="C177" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D177" s="16"/>
       <c r="E177" s="16"/>
     </row>
@@ -2608,7 +2962,9 @@
       <c r="B178" s="13">
         <v>176</v>
       </c>
-      <c r="C178" s="15"/>
+      <c r="C178" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D178" s="16"/>
       <c r="E178" s="16"/>
     </row>
@@ -2617,7 +2973,9 @@
       <c r="B179" s="13">
         <v>177</v>
       </c>
-      <c r="C179" s="15"/>
+      <c r="C179" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D179" s="16"/>
       <c r="E179" s="16"/>
     </row>
@@ -2626,7 +2984,9 @@
       <c r="B180" s="13">
         <v>178</v>
       </c>
-      <c r="C180" s="15"/>
+      <c r="C180" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D180" s="16"/>
       <c r="E180" s="16"/>
     </row>
@@ -2635,7 +2995,9 @@
       <c r="B181" s="13">
         <v>179</v>
       </c>
-      <c r="C181" s="15"/>
+      <c r="C181" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D181" s="16"/>
       <c r="E181" s="16"/>
     </row>
@@ -2644,7 +3006,9 @@
       <c r="B182" s="13">
         <v>180</v>
       </c>
-      <c r="C182" s="15"/>
+      <c r="C182" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D182" s="16"/>
       <c r="E182" s="16"/>
     </row>
@@ -2653,7 +3017,9 @@
       <c r="B183" s="13">
         <v>181</v>
       </c>
-      <c r="C183" s="15"/>
+      <c r="C183" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D183" s="16"/>
       <c r="E183" s="16"/>
     </row>
@@ -2662,7 +3028,9 @@
       <c r="B184" s="13">
         <v>182</v>
       </c>
-      <c r="C184" s="15"/>
+      <c r="C184" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D184" s="16"/>
       <c r="E184" s="16"/>
     </row>
@@ -2671,7 +3039,9 @@
       <c r="B185" s="13">
         <v>183</v>
       </c>
-      <c r="C185" s="15"/>
+      <c r="C185" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D185" s="16"/>
       <c r="E185" s="16"/>
     </row>
@@ -2680,7 +3050,9 @@
       <c r="B186" s="13">
         <v>184</v>
       </c>
-      <c r="C186" s="15"/>
+      <c r="C186" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D186" s="16"/>
       <c r="E186" s="16"/>
     </row>
@@ -2689,7 +3061,9 @@
       <c r="B187" s="13">
         <v>185</v>
       </c>
-      <c r="C187" s="15"/>
+      <c r="C187" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D187" s="16"/>
       <c r="E187" s="16"/>
     </row>
@@ -2698,7 +3072,9 @@
       <c r="B188" s="13">
         <v>186</v>
       </c>
-      <c r="C188" s="15"/>
+      <c r="C188" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D188" s="16"/>
       <c r="E188" s="16"/>
     </row>
@@ -2707,7 +3083,9 @@
       <c r="B189" s="14">
         <v>187</v>
       </c>
-      <c r="C189" s="15"/>
+      <c r="C189" s="15" t="s">
+        <v>0</v>
+      </c>
       <c r="D189" s="16"/>
       <c r="E189" s="16"/>
     </row>
@@ -2771,7 +3149,7 @@
   <sheetProtection password="F5E8" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="PILAS!!!!" error="Solo puede colocar A,B ó C." sqref="C3:C189">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="PILAS!!!!" error="Solo puede colocar A,B ó C." sqref="C3:C189" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$W$2:$W$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -2782,59 +3160,59 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AW62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" style="25" customWidth="1"/>
-    <col min="2" max="2" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.28515625" style="25" customWidth="1"/>
-    <col min="5" max="5" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.5703125" style="25" customWidth="1"/>
-    <col min="8" max="8" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.28515625" style="25" customWidth="1"/>
-    <col min="14" max="14" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.140625" style="25" customWidth="1"/>
-    <col min="17" max="17" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2" style="25" customWidth="1"/>
-    <col min="20" max="20" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.28515625" style="25" customWidth="1"/>
-    <col min="23" max="23" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="1.42578125" style="25" customWidth="1"/>
-    <col min="26" max="26" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2" style="25" customWidth="1"/>
-    <col min="29" max="29" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3" style="25" customWidth="1"/>
-    <col min="32" max="32" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="2.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="2.28515625" style="25" customWidth="1"/>
-    <col min="35" max="35" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="2.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.42578125" style="25" customWidth="1"/>
-    <col min="38" max="38" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="3.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="3.42578125" style="25" customWidth="1"/>
-    <col min="41" max="41" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="3.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="3.42578125" style="25" customWidth="1"/>
-    <col min="44" max="44" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="3.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="3.42578125" style="25" customWidth="1"/>
-    <col min="47" max="47" width="4" style="25" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="3.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="11.42578125" style="25" customWidth="1"/>
-    <col min="50" max="16384" width="11.42578125" style="25" hidden="1"/>
+    <col min="1" max="1" width="7" style="24" customWidth="1"/>
+    <col min="2" max="2" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.28515625" style="24" customWidth="1"/>
+    <col min="5" max="5" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" style="24" customWidth="1"/>
+    <col min="8" max="8" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.28515625" style="24" customWidth="1"/>
+    <col min="14" max="14" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.140625" style="24" customWidth="1"/>
+    <col min="17" max="17" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2" style="24" customWidth="1"/>
+    <col min="20" max="20" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.28515625" style="24" customWidth="1"/>
+    <col min="23" max="23" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1.42578125" style="24" customWidth="1"/>
+    <col min="26" max="26" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="2" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2" style="24" customWidth="1"/>
+    <col min="29" max="29" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3" style="24" customWidth="1"/>
+    <col min="32" max="32" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="2.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="2.28515625" style="24" customWidth="1"/>
+    <col min="35" max="35" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="2.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.42578125" style="24" customWidth="1"/>
+    <col min="38" max="38" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="3.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="3.42578125" style="24" customWidth="1"/>
+    <col min="41" max="41" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="3.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3.42578125" style="24" customWidth="1"/>
+    <col min="44" max="44" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="3.42578125" style="24" customWidth="1"/>
+    <col min="47" max="47" width="4" style="24" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="3.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.42578125" style="24" customWidth="1"/>
+    <col min="50" max="16384" width="11.42578125" style="24" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.2">
@@ -2972,7 +3350,7 @@
       </c>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="21" t="s">
+      <c r="U3" s="20" t="s">
         <v>6</v>
       </c>
       <c r="V3" s="9"/>
@@ -3029,7 +3407,7 @@
       </c>
       <c r="C4" s="3">
         <f>IF(Respuestas!C22="A",2,IF(Respuestas!C22="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="2">
@@ -3037,7 +3415,7 @@
       </c>
       <c r="F4" s="3">
         <f>IF(Respuestas!C5="B",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="2">
@@ -3045,7 +3423,7 @@
       </c>
       <c r="I4" s="3">
         <f>IF(Respuestas!C6="A",2,IF(Respuestas!C6="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="8"/>
       <c r="K4" s="2">
@@ -3053,7 +3431,7 @@
       </c>
       <c r="L4" s="3">
         <f>IF(Respuestas!C7="C",2,IF(Respuestas!C7="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="2">
@@ -3069,13 +3447,13 @@
       </c>
       <c r="R4" s="3">
         <f>IF(Respuestas!C10="C",2,IF(Respuestas!C10="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" s="8"/>
-      <c r="T4" s="18">
+      <c r="T4" s="17">
         <v>9</v>
       </c>
-      <c r="U4" s="22">
+      <c r="U4" s="21">
         <f>IF(Respuestas!C11="A",2,IF(Respuestas!C11="B",1,0))</f>
         <v>0</v>
       </c>
@@ -3101,7 +3479,7 @@
       </c>
       <c r="AD4" s="3">
         <f>IF(Respuestas!C14="C",2,IF(Respuestas!C14="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4" s="8"/>
       <c r="AF4" s="2">
@@ -3117,7 +3495,7 @@
       </c>
       <c r="AJ4" s="3">
         <f>IF(Respuestas!C16="A",2,IF(Respuestas!C16="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK4" s="8"/>
       <c r="AL4" s="2">
@@ -3133,7 +3511,7 @@
       </c>
       <c r="AP4" s="3">
         <f>IF(Respuestas!C19="C",2,IF(Respuestas!C19="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ4" s="8"/>
       <c r="AR4" s="2">
@@ -3141,7 +3519,7 @@
       </c>
       <c r="AS4" s="3">
         <f>IF(Respuestas!C20="C",2,IF(Respuestas!C20="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT4" s="8"/>
       <c r="AU4" s="2">
@@ -3160,7 +3538,7 @@
       </c>
       <c r="C5" s="5">
         <f>IF(Respuestas!C23="B",1,IF(Respuestas!C23="C",2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="4">
@@ -3176,7 +3554,7 @@
       </c>
       <c r="I5" s="5">
         <f>IF(Respuestas!C25="C",2,IF(Respuestas!C25="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="4">
@@ -3184,7 +3562,7 @@
       </c>
       <c r="L5" s="5">
         <f>IF(Respuestas!C8="A",2,IF(Respuestas!C8="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="4">
@@ -3192,7 +3570,7 @@
       </c>
       <c r="O5" s="5">
         <f>IF(Respuestas!C27="A",2,IF(Respuestas!C27="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="4">
@@ -3203,12 +3581,12 @@
         <v>0</v>
       </c>
       <c r="S5" s="8"/>
-      <c r="T5" s="19">
+      <c r="T5" s="18">
         <v>28</v>
       </c>
-      <c r="U5" s="23">
+      <c r="U5" s="22">
         <f>IF(Respuestas!C30="C",2,IF(Respuestas!C30="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5" s="8"/>
       <c r="W5" s="4">
@@ -3224,7 +3602,7 @@
       </c>
       <c r="AA5" s="5">
         <f>IF(Respuestas!C32="A",2,IF(Respuestas!C32="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB5" s="8"/>
       <c r="AC5" s="4">
@@ -3240,7 +3618,7 @@
       </c>
       <c r="AG5" s="5">
         <f>IF(Respuestas!C34="A",2,IF(Respuestas!C34="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" s="8"/>
       <c r="AI5" s="4">
@@ -3248,7 +3626,7 @@
       </c>
       <c r="AJ5" s="5">
         <f>IF(Respuestas!C17="C",2,IF(Respuestas!C17="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" s="8"/>
       <c r="AL5" s="4">
@@ -3256,7 +3634,7 @@
       </c>
       <c r="AM5" s="5">
         <f>IF(Respuestas!C37="C",2,IF(Respuestas!C37="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN5" s="8"/>
       <c r="AO5" s="4">
@@ -3264,7 +3642,7 @@
       </c>
       <c r="AP5" s="5">
         <f>IF(Respuestas!C38="A",2,IF(Respuestas!C38="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ5" s="8"/>
       <c r="AR5" s="4">
@@ -3272,7 +3650,7 @@
       </c>
       <c r="AS5" s="5">
         <f>IF(Respuestas!C39="C",2,IF(Respuestas!C39="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT5" s="8"/>
       <c r="AU5" s="4">
@@ -3315,7 +3693,7 @@
       </c>
       <c r="L6" s="5">
         <f>IF(Respuestas!C26="C",2,IF(Respuestas!C26="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="4">
@@ -3334,10 +3712,10 @@
         <v>0</v>
       </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="19">
+      <c r="T6" s="18">
         <v>47</v>
       </c>
-      <c r="U6" s="23">
+      <c r="U6" s="22">
         <f>IF(Respuestas!C49="A",2,IF(Respuestas!C49="B",1,0))</f>
         <v>0</v>
       </c>
@@ -3347,7 +3725,7 @@
       </c>
       <c r="X6" s="5">
         <f>IF(Respuestas!C50="A",2,IF(Respuestas!C50="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="8"/>
       <c r="Z6" s="4">
@@ -3355,7 +3733,7 @@
       </c>
       <c r="AA6" s="5">
         <f>IF(Respuestas!C51="C",2,IF(Respuestas!C51="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6" s="8"/>
       <c r="AC6" s="4">
@@ -3379,7 +3757,7 @@
       </c>
       <c r="AJ6" s="5">
         <f>IF(Respuestas!C35="A",2,IF(Respuestas!C35="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" s="8"/>
       <c r="AL6" s="4">
@@ -3395,7 +3773,7 @@
       </c>
       <c r="AP6" s="5">
         <f>IF(Respuestas!C57="A",2,IF(Respuestas!C57="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ6" s="8"/>
       <c r="AR6" s="4">
@@ -3403,7 +3781,7 @@
       </c>
       <c r="AS6" s="5">
         <f>IF(Respuestas!C58="A",2,IF(Respuestas!C58="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT6" s="8"/>
       <c r="AU6" s="4">
@@ -3411,7 +3789,7 @@
       </c>
       <c r="AV6" s="5">
         <f>IF(Respuestas!C59="A",2,IF(Respuestas!C59="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" s="8"/>
     </row>
@@ -3422,7 +3800,7 @@
       </c>
       <c r="C7" s="5">
         <f>IF(Respuestas!C60="B",1,IF(Respuestas!C60="C",2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="4">
@@ -3446,7 +3824,7 @@
       </c>
       <c r="L7" s="5">
         <f>IF(Respuestas!C45="C",2,IF(Respuestas!C45="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="4">
@@ -3462,15 +3840,15 @@
       </c>
       <c r="R7" s="5">
         <f>IF(Respuestas!C67="C",2,IF(Respuestas!C67="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" s="8"/>
-      <c r="T7" s="19">
+      <c r="T7" s="18">
         <v>66</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="22">
         <f>IF(Respuestas!C68="C",2,IF(Respuestas!C68="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="8"/>
       <c r="W7" s="4">
@@ -3494,7 +3872,7 @@
       </c>
       <c r="AD7" s="5">
         <f>IF(Respuestas!C71="A",2,IF(Respuestas!C71="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="8"/>
       <c r="AF7" s="4">
@@ -3502,7 +3880,7 @@
       </c>
       <c r="AG7" s="5">
         <f>IF(Respuestas!C72="A",2,IF(Respuestas!C72="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" s="8"/>
       <c r="AI7" s="4">
@@ -3526,7 +3904,7 @@
       </c>
       <c r="AP7" s="5">
         <f>IF(Respuestas!C75="A",2,IF(Respuestas!C75="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ7" s="8"/>
       <c r="AR7" s="4">
@@ -3534,7 +3912,7 @@
       </c>
       <c r="AS7" s="5">
         <f>IF(Respuestas!C77="A",2,IF(Respuestas!C77="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT7" s="8"/>
       <c r="AU7" s="4">
@@ -3542,7 +3920,7 @@
       </c>
       <c r="AV7" s="5">
         <f>IF(Respuestas!C78="A",2,IF(Respuestas!C78="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW7" s="8"/>
     </row>
@@ -3553,7 +3931,7 @@
       </c>
       <c r="C8" s="5">
         <f>IF(Respuestas!C79="A",2,IF(Respuestas!C79="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="4">
@@ -3577,7 +3955,7 @@
       </c>
       <c r="L8" s="5">
         <f>IF(Respuestas!C64="A",2,IF(Respuestas!C64="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="4">
@@ -3585,7 +3963,7 @@
       </c>
       <c r="O8" s="5">
         <f>IF(Respuestas!C47="A",2,IF(Respuestas!C47="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="4">
@@ -3593,15 +3971,15 @@
       </c>
       <c r="R8" s="5">
         <f>IF(Respuestas!C85="A",2,IF(Respuestas!C85="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="8"/>
-      <c r="T8" s="19">
+      <c r="T8" s="18">
         <v>84</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="22">
         <f>IF(Respuestas!C86="C",2,IF(Respuestas!C86="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="8"/>
       <c r="W8" s="4">
@@ -3609,7 +3987,7 @@
       </c>
       <c r="X8" s="5">
         <f>IF(Respuestas!C88="C",2,IF(Respuestas!C88="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="8"/>
       <c r="Z8" s="4">
@@ -3617,7 +3995,7 @@
       </c>
       <c r="AA8" s="5">
         <f>IF(Respuestas!C89="A",2,IF(Respuestas!C89="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="8"/>
       <c r="AC8" s="4">
@@ -3649,7 +4027,7 @@
       </c>
       <c r="AM8" s="5">
         <f>IF(Respuestas!C93="A",2,IF(Respuestas!C93="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN8" s="8"/>
       <c r="AO8" s="4">
@@ -3657,7 +4035,7 @@
       </c>
       <c r="AP8" s="5">
         <f>IF(Respuestas!C76="C",2,IF(Respuestas!C76="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ8" s="8"/>
       <c r="AR8" s="4">
@@ -3665,7 +4043,7 @@
       </c>
       <c r="AS8" s="5">
         <f>IF(Respuestas!C95="A",2,IF(Respuestas!C95="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT8" s="8"/>
       <c r="AU8" s="4">
@@ -3692,7 +4070,7 @@
       </c>
       <c r="F9" s="5">
         <f>IF(Respuestas!C62="C",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="4">
@@ -3708,7 +4086,7 @@
       </c>
       <c r="L9" s="5">
         <f>IF(Respuestas!C83="C",2,IF(Respuestas!C83="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="4">
@@ -3724,15 +4102,15 @@
       </c>
       <c r="R9" s="5">
         <f>IF(Respuestas!C104="A",2,IF(Respuestas!C104="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" s="8"/>
-      <c r="T9" s="19">
+      <c r="T9" s="18">
         <v>85</v>
       </c>
-      <c r="U9" s="23">
+      <c r="U9" s="22">
         <f>IF(Respuestas!C87="C",2,IF(Respuestas!C87="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="8"/>
       <c r="W9" s="4">
@@ -3740,7 +4118,7 @@
       </c>
       <c r="X9" s="5">
         <f>IF(Respuestas!C107="A",2,IF(Respuestas!C107="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="8"/>
       <c r="Z9" s="4">
@@ -3804,7 +4182,7 @@
       </c>
       <c r="AV9" s="5">
         <f>IF(Respuestas!C115="A",2,IF(Respuestas!C115="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW9" s="8"/>
     </row>
@@ -3815,7 +4193,7 @@
       </c>
       <c r="C10" s="5">
         <f>IF(Respuestas!C117="A",2,IF(Respuestas!C117="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="4">
@@ -3847,7 +4225,7 @@
       </c>
       <c r="O10" s="5">
         <f>IF(Respuestas!C66="C",2,IF(Respuestas!C66="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" s="8"/>
       <c r="Q10" s="4">
@@ -3858,10 +4236,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="8"/>
-      <c r="T10" s="19">
+      <c r="T10" s="18">
         <v>103</v>
       </c>
-      <c r="U10" s="23">
+      <c r="U10" s="22">
         <f>IF(Respuestas!C105="C",2,IF(Respuestas!C105="B",1,0))</f>
         <v>0</v>
       </c>
@@ -3879,7 +4257,7 @@
       </c>
       <c r="AA10" s="5">
         <f>IF(Respuestas!C127="A",2,IF(Respuestas!C127="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" s="8"/>
       <c r="AC10" s="4">
@@ -3887,7 +4265,7 @@
       </c>
       <c r="AD10" s="5">
         <f>IF(Respuestas!C128="A",2,IF(Respuestas!C128="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE10" s="8"/>
       <c r="AF10" s="4">
@@ -3903,7 +4281,7 @@
       </c>
       <c r="AJ10" s="5">
         <f>IF(Respuestas!C73="C",2,IF(Respuestas!C73="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK10" s="8"/>
       <c r="AL10" s="4">
@@ -3946,7 +4324,7 @@
       </c>
       <c r="C11" s="5">
         <f>IF(Respuestas!C136="A",2,IF(Respuestas!C136="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="4">
@@ -3954,7 +4332,7 @@
       </c>
       <c r="F11" s="5">
         <f>IF(Respuestas!C81="C",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="4">
@@ -3962,7 +4340,7 @@
       </c>
       <c r="I11" s="5">
         <f>IF(Respuestas!C119="A",2,IF(Respuestas!C119="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="8"/>
       <c r="K11" s="4">
@@ -3978,7 +4356,7 @@
       </c>
       <c r="O11" s="5">
         <f>IF(Respuestas!C84="A",2,IF(Respuestas!C84="B",1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="4">
@@ -3986,15 +4364,15 @@
       </c>
       <c r="R11" s="5">
         <f>IF(Respuestas!C142="A",2,IF(Respuestas!C142="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" s="8"/>
-      <c r="T11" s="19">
+      <c r="T11" s="18">
         <v>104</v>
       </c>
-      <c r="U11" s="23">
+      <c r="U11" s="22">
         <f>IF(Respuestas!C106="A",2,IF(Respuestas!C106="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" s="8"/>
       <c r="W11" s="4">
@@ -4002,7 +4380,7 @@
       </c>
       <c r="X11" s="5">
         <f>IF(Respuestas!C144="A",2,IF(Respuestas!C144="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="4">
@@ -4010,7 +4388,7 @@
       </c>
       <c r="AA11" s="5">
         <f>IF(Respuestas!C145="A",2,IF(Respuestas!C145="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" s="8"/>
       <c r="AC11" s="4">
@@ -4018,7 +4396,7 @@
       </c>
       <c r="AD11" s="5">
         <f>IF(Respuestas!C146="A",2,IF(Respuestas!C146="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" s="8"/>
       <c r="AF11" s="4">
@@ -4026,7 +4404,7 @@
       </c>
       <c r="AG11" s="5">
         <f>IF(Respuestas!C148="A",2,IF(Respuestas!C148="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" s="8"/>
       <c r="AI11" s="4">
@@ -4034,7 +4412,7 @@
       </c>
       <c r="AJ11" s="5">
         <f>IF(Respuestas!C92="A",2,IF(Respuestas!C92="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK11" s="8"/>
       <c r="AL11" s="4">
@@ -4042,7 +4420,7 @@
       </c>
       <c r="AM11" s="5">
         <f>IF(Respuestas!C150="A",2,IF(Respuestas!C150="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN11" s="8"/>
       <c r="AO11" s="4">
@@ -4058,7 +4436,7 @@
       </c>
       <c r="AS11" s="5">
         <f>IF(Respuestas!C133="A",2,IF(Respuestas!C133="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT11" s="8"/>
       <c r="AU11" s="4">
@@ -4066,7 +4444,7 @@
       </c>
       <c r="AV11" s="5">
         <f>IF(Respuestas!C134="A",2,IF(Respuestas!C134="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW11" s="8"/>
     </row>
@@ -4093,7 +4471,7 @@
       </c>
       <c r="I12" s="5">
         <f>IF(Respuestas!C120="A",2,IF(Respuestas!C120="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="4">
@@ -4101,7 +4479,7 @@
       </c>
       <c r="L12" s="5">
         <f>IF(Respuestas!C140="A",2,IF(Respuestas!C140="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="8"/>
       <c r="N12" s="4">
@@ -4109,7 +4487,7 @@
       </c>
       <c r="O12" s="5">
         <f>IF(Respuestas!C103="A",2,IF(Respuestas!C103="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="4">
@@ -4117,15 +4495,15 @@
       </c>
       <c r="R12" s="5">
         <f>IF(Respuestas!C161="A",2,IF(Respuestas!C161="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" s="8"/>
-      <c r="T12" s="19">
+      <c r="T12" s="18">
         <v>122</v>
       </c>
-      <c r="U12" s="23">
+      <c r="U12" s="22">
         <f>IF(Respuestas!C124="A",2,IF(Respuestas!C124="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V12" s="8"/>
       <c r="W12" s="4">
@@ -4149,7 +4527,7 @@
       </c>
       <c r="AD12" s="5">
         <f>IF(Respuestas!C147="A",2,IF(Respuestas!C147="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE12" s="8"/>
       <c r="AF12" s="4">
@@ -4157,7 +4535,7 @@
       </c>
       <c r="AG12" s="5">
         <f>IF(Respuestas!C167="A",2,IF(Respuestas!C167="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" s="8"/>
       <c r="AI12" s="4">
@@ -4165,7 +4543,7 @@
       </c>
       <c r="AJ12" s="5">
         <f>IF(Respuestas!C111="A",2,IF(Respuestas!C111="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK12" s="8"/>
       <c r="AL12" s="4">
@@ -4173,7 +4551,7 @@
       </c>
       <c r="AM12" s="5">
         <f>IF(Respuestas!C169="A",2,IF(Respuestas!C169="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN12" s="8"/>
       <c r="AO12" s="4">
@@ -4181,7 +4559,7 @@
       </c>
       <c r="AP12" s="5">
         <f>IF(Respuestas!C151="A",2,IF(Respuestas!C151="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ12" s="8"/>
       <c r="AR12" s="4">
@@ -4208,7 +4586,7 @@
       </c>
       <c r="C13" s="7">
         <f>IF(Respuestas!C174="A",2,IF(Respuestas!C174="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="4">
@@ -4216,7 +4594,7 @@
       </c>
       <c r="F13" s="5">
         <f>IF(Respuestas!C118="A",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="4">
@@ -4232,7 +4610,7 @@
       </c>
       <c r="L13" s="5">
         <f>IF(Respuestas!C158="A",2,IF(Respuestas!C158="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="8"/>
       <c r="N13" s="4">
@@ -4248,15 +4626,15 @@
       </c>
       <c r="R13" s="7">
         <f>IF(Respuestas!C180="A",2,IF(Respuestas!C180="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13" s="8"/>
-      <c r="T13" s="19">
+      <c r="T13" s="18">
         <v>123</v>
       </c>
-      <c r="U13" s="23">
+      <c r="U13" s="22">
         <f>IF(Respuestas!C125="A",2,IF(Respuestas!C125="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" s="8"/>
       <c r="W13" s="6">
@@ -4264,7 +4642,7 @@
       </c>
       <c r="X13" s="7">
         <f>IF(Respuestas!C182="A",2,IF(Respuestas!C182="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="8"/>
       <c r="Z13" s="6">
@@ -4272,7 +4650,7 @@
       </c>
       <c r="AA13" s="7">
         <f>IF(Respuestas!C183="A",2,IF(Respuestas!C183="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13" s="8"/>
       <c r="AC13" s="4">
@@ -4280,7 +4658,7 @@
       </c>
       <c r="AD13" s="5">
         <f>IF(Respuestas!C165="A",2,IF(Respuestas!C165="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE13" s="8"/>
       <c r="AF13" s="6">
@@ -4288,7 +4666,7 @@
       </c>
       <c r="AG13" s="7">
         <f>IF(Respuestas!C186="A",2,IF(Respuestas!C186="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" s="8"/>
       <c r="AI13" s="4">
@@ -4296,7 +4674,7 @@
       </c>
       <c r="AJ13" s="5">
         <f>IF(Respuestas!C130="A",2,IF(Respuestas!C130="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK13" s="8"/>
       <c r="AL13" s="6">
@@ -4312,7 +4690,7 @@
       </c>
       <c r="AP13" s="7">
         <f>IF(Respuestas!C170="A",2,IF(Respuestas!C170="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ13" s="8"/>
       <c r="AR13" s="6">
@@ -4320,7 +4698,7 @@
       </c>
       <c r="AS13" s="7">
         <f>IF(Respuestas!C171="A",2,IF(Respuestas!C171="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT13" s="8"/>
       <c r="AU13" s="4">
@@ -4328,7 +4706,7 @@
       </c>
       <c r="AV13" s="5">
         <f>IF(Respuestas!C153="A",2,IF(Respuestas!C153="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW13" s="8"/>
     </row>
@@ -4350,7 +4728,7 @@
       </c>
       <c r="I14" s="5">
         <f>IF(Respuestas!C139="A",2,IF(Respuestas!C139="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="4">
@@ -4358,7 +4736,7 @@
       </c>
       <c r="L14" s="5">
         <f>IF(Respuestas!C159="A",2,IF(Respuestas!C159="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="8"/>
       <c r="N14" s="4">
@@ -4372,12 +4750,12 @@
       <c r="Q14" s="8"/>
       <c r="R14" s="8"/>
       <c r="S14" s="8"/>
-      <c r="T14" s="19">
+      <c r="T14" s="18">
         <v>141</v>
       </c>
-      <c r="U14" s="23">
+      <c r="U14" s="22">
         <f>IF(Respuestas!C143="A",2,IF(Respuestas!C143="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
@@ -4402,7 +4780,7 @@
       </c>
       <c r="AJ14" s="5">
         <f>IF(Respuestas!C149="A",2,IF(Respuestas!C149="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK14" s="8"/>
       <c r="AL14" s="8"/>
@@ -4433,7 +4811,7 @@
       </c>
       <c r="F15" s="5">
         <f>IF(Respuestas!C156="A",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="4">
@@ -4449,7 +4827,7 @@
       </c>
       <c r="L15" s="5">
         <f>IF(Respuestas!C177="A",2,IF(Respuestas!C177="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="8"/>
       <c r="N15" s="4">
@@ -4457,16 +4835,16 @@
       </c>
       <c r="O15" s="5">
         <f>IF(Respuestas!C160="A",2,IF(Respuestas!C160="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
-      <c r="T15" s="19">
+      <c r="T15" s="18">
         <v>160</v>
       </c>
-      <c r="U15" s="23">
+      <c r="U15" s="22">
         <f>IF(Respuestas!C162="C",2,IF(Respuestas!C162="B",1,0))</f>
         <v>0</v>
       </c>
@@ -4510,7 +4888,7 @@
       </c>
       <c r="AV15" s="5">
         <f>IF(Respuestas!C172="A",2,IF(Respuestas!C172="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW15" s="8"/>
     </row>
@@ -4524,7 +4902,7 @@
       </c>
       <c r="F16" s="7">
         <f>IF(Respuestas!C175="A",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="6">
@@ -4532,7 +4910,7 @@
       </c>
       <c r="I16" s="7">
         <f>IF(Respuestas!C176="A",2,IF(Respuestas!C176="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="6">
@@ -4540,7 +4918,7 @@
       </c>
       <c r="L16" s="7">
         <f>IF(Respuestas!C178="A",2,IF(Respuestas!C178="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="8"/>
       <c r="N16" s="6">
@@ -4548,18 +4926,18 @@
       </c>
       <c r="O16" s="7">
         <f>IF(Respuestas!C179="A",2,IF(Respuestas!C179="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
-      <c r="T16" s="20">
+      <c r="T16" s="19">
         <v>179</v>
       </c>
-      <c r="U16" s="24">
+      <c r="U16" s="23">
         <f>IF(Respuestas!C181="A",2,IF(Respuestas!C181="B",1,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
@@ -4658,136 +5036,136 @@
     </row>
     <row r="18" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
-      <c r="B18" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29"/>
+      <c r="B18" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="47"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="29"/>
+      <c r="F18" s="47"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="29"/>
+      <c r="H18" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="47"/>
       <c r="J18" s="10"/>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="29"/>
+      <c r="L18" s="47"/>
       <c r="M18" s="10"/>
-      <c r="N18" s="28" t="s">
+      <c r="N18" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="29"/>
+      <c r="O18" s="47"/>
       <c r="P18" s="10"/>
-      <c r="Q18" s="28" t="s">
+      <c r="Q18" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="R18" s="29"/>
+      <c r="R18" s="47"/>
       <c r="S18" s="10"/>
-      <c r="T18" s="28" t="s">
+      <c r="T18" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="U18" s="29"/>
+      <c r="U18" s="47"/>
       <c r="V18" s="10"/>
-      <c r="W18" s="28" t="s">
+      <c r="W18" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="X18" s="29"/>
+      <c r="X18" s="47"/>
       <c r="Y18" s="10"/>
-      <c r="Z18" s="28" t="s">
+      <c r="Z18" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="AA18" s="29"/>
+      <c r="AA18" s="47"/>
       <c r="AB18" s="10"/>
-      <c r="AC18" s="28" t="s">
+      <c r="AC18" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="AD18" s="29"/>
+      <c r="AD18" s="47"/>
       <c r="AE18" s="10"/>
-      <c r="AF18" s="28" t="s">
+      <c r="AF18" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="AG18" s="29"/>
+      <c r="AG18" s="47"/>
       <c r="AH18" s="10"/>
-      <c r="AI18" s="28" t="s">
+      <c r="AI18" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="AJ18" s="29"/>
+      <c r="AJ18" s="47"/>
       <c r="AK18" s="10"/>
-      <c r="AL18" s="28" t="s">
+      <c r="AL18" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="AM18" s="29"/>
+      <c r="AM18" s="47"/>
       <c r="AN18" s="10"/>
-      <c r="AO18" s="28" t="s">
+      <c r="AO18" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="AP18" s="29"/>
+      <c r="AP18" s="47"/>
       <c r="AQ18" s="10"/>
-      <c r="AR18" s="28" t="s">
+      <c r="AR18" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="AS18" s="29"/>
+      <c r="AS18" s="47"/>
       <c r="AT18" s="10"/>
-      <c r="AU18" s="28" t="s">
+      <c r="AU18" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AV18" s="29"/>
+      <c r="AV18" s="47"/>
       <c r="AW18" s="8"/>
     </row>
     <row r="19" spans="1:49" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="49"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="31"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="49"/>
       <c r="J19" s="10"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="31"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="49"/>
       <c r="M19" s="10"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="31"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="49"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="31"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="49"/>
       <c r="S19" s="10"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="31"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="49"/>
       <c r="V19" s="10"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="31"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="49"/>
       <c r="Y19" s="10"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="31"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="49"/>
       <c r="AB19" s="10"/>
-      <c r="AC19" s="30"/>
-      <c r="AD19" s="31"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="49"/>
       <c r="AE19" s="10"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="31"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="49"/>
       <c r="AH19" s="10"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="31"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="49"/>
       <c r="AK19" s="10"/>
-      <c r="AL19" s="30"/>
-      <c r="AM19" s="31"/>
+      <c r="AL19" s="48"/>
+      <c r="AM19" s="49"/>
       <c r="AN19" s="10"/>
-      <c r="AO19" s="30"/>
-      <c r="AP19" s="31"/>
+      <c r="AO19" s="48"/>
+      <c r="AP19" s="49"/>
       <c r="AQ19" s="10"/>
-      <c r="AR19" s="30"/>
-      <c r="AS19" s="31"/>
+      <c r="AR19" s="48"/>
+      <c r="AS19" s="49"/>
       <c r="AT19" s="10"/>
-      <c r="AU19" s="30"/>
-      <c r="AV19" s="31"/>
+      <c r="AU19" s="48"/>
+      <c r="AV19" s="49"/>
       <c r="AW19" s="8"/>
     </row>
     <row r="20" spans="1:49" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -4843,152 +5221,152 @@
     </row>
     <row r="21" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
-      <c r="B21" s="32">
+      <c r="B21" s="42">
         <f>SUM(C4:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="33"/>
+        <v>14</v>
+      </c>
+      <c r="C21" s="43"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="32">
+      <c r="E21" s="42">
         <f>SUM(F4:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="33"/>
+        <v>6</v>
+      </c>
+      <c r="F21" s="43"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="32">
+      <c r="H21" s="42">
         <f>SUM(I4:I16)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="I21" s="43"/>
       <c r="J21" s="8"/>
-      <c r="K21" s="32">
+      <c r="K21" s="42">
         <f>SUM(L4:L16)</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="33"/>
+        <v>22</v>
+      </c>
+      <c r="L21" s="43"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="32">
+      <c r="N21" s="42">
         <f>SUM(O4:O16)</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="33"/>
+        <v>13</v>
+      </c>
+      <c r="O21" s="43"/>
       <c r="P21" s="8"/>
-      <c r="Q21" s="32">
+      <c r="Q21" s="42">
         <f>SUM(R4:R13)</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="33"/>
+        <v>13</v>
+      </c>
+      <c r="R21" s="43"/>
       <c r="S21" s="8"/>
-      <c r="T21" s="32">
+      <c r="T21" s="42">
         <f>SUM(U4:U16)</f>
-        <v>0</v>
-      </c>
-      <c r="U21" s="33"/>
+        <v>18</v>
+      </c>
+      <c r="U21" s="43"/>
       <c r="V21" s="8"/>
-      <c r="W21" s="32">
+      <c r="W21" s="42">
         <f>SUM(X4:X13)</f>
-        <v>0</v>
-      </c>
-      <c r="X21" s="33"/>
+        <v>10</v>
+      </c>
+      <c r="X21" s="43"/>
       <c r="Y21" s="8"/>
-      <c r="Z21" s="32">
+      <c r="Z21" s="42">
         <f>SUM(AA4:AA13)</f>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="33"/>
+        <v>12</v>
+      </c>
+      <c r="AA21" s="43"/>
       <c r="AB21" s="8"/>
-      <c r="AC21" s="32">
+      <c r="AC21" s="42">
         <f>SUM(AD4:AD16)</f>
-        <v>0</v>
-      </c>
-      <c r="AD21" s="33"/>
+        <v>11</v>
+      </c>
+      <c r="AD21" s="43"/>
       <c r="AE21" s="8"/>
-      <c r="AF21" s="32">
+      <c r="AF21" s="42">
         <f>SUM(AG4:AG13)</f>
-        <v>0</v>
-      </c>
-      <c r="AG21" s="33"/>
+        <v>10</v>
+      </c>
+      <c r="AG21" s="43"/>
       <c r="AH21" s="8"/>
-      <c r="AI21" s="32">
+      <c r="AI21" s="42">
         <f>SUM(AJ4:AJ16)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="33"/>
+        <v>14</v>
+      </c>
+      <c r="AJ21" s="43"/>
       <c r="AK21" s="8"/>
-      <c r="AL21" s="32">
+      <c r="AL21" s="42">
         <f>SUM(AM4:AM13)</f>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="33"/>
+        <v>8</v>
+      </c>
+      <c r="AM21" s="43"/>
       <c r="AN21" s="8"/>
-      <c r="AO21" s="32">
+      <c r="AO21" s="42">
         <f>SUM(AP4:AP13)</f>
-        <v>0</v>
-      </c>
-      <c r="AP21" s="33"/>
+        <v>14</v>
+      </c>
+      <c r="AP21" s="43"/>
       <c r="AQ21" s="8"/>
-      <c r="AR21" s="32">
+      <c r="AR21" s="42">
         <f>SUM(AS4:AS13)</f>
-        <v>0</v>
-      </c>
-      <c r="AS21" s="33"/>
+        <v>14</v>
+      </c>
+      <c r="AS21" s="43"/>
       <c r="AT21" s="8"/>
-      <c r="AU21" s="32">
+      <c r="AU21" s="42">
         <f>SUM(AV4:AV16)</f>
-        <v>0</v>
-      </c>
-      <c r="AV21" s="33"/>
+        <v>10</v>
+      </c>
+      <c r="AV21" s="43"/>
       <c r="AW21" s="8"/>
     </row>
     <row r="22" spans="1:49" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="35"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
       <c r="J22" s="8"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="35"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="45"/>
       <c r="M22" s="8"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="35"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="45"/>
       <c r="P22" s="8"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="35"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="45"/>
       <c r="S22" s="8"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="45"/>
       <c r="V22" s="8"/>
-      <c r="W22" s="34"/>
-      <c r="X22" s="35"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="45"/>
       <c r="Y22" s="8"/>
-      <c r="Z22" s="34"/>
-      <c r="AA22" s="35"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="45"/>
       <c r="AB22" s="8"/>
-      <c r="AC22" s="34"/>
-      <c r="AD22" s="35"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="45"/>
       <c r="AE22" s="8"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="35"/>
+      <c r="AF22" s="44"/>
+      <c r="AG22" s="45"/>
       <c r="AH22" s="8"/>
-      <c r="AI22" s="34"/>
-      <c r="AJ22" s="35"/>
+      <c r="AI22" s="44"/>
+      <c r="AJ22" s="45"/>
       <c r="AK22" s="8"/>
-      <c r="AL22" s="34"/>
-      <c r="AM22" s="35"/>
+      <c r="AL22" s="44"/>
+      <c r="AM22" s="45"/>
       <c r="AN22" s="8"/>
-      <c r="AO22" s="34"/>
-      <c r="AP22" s="35"/>
+      <c r="AO22" s="44"/>
+      <c r="AP22" s="45"/>
       <c r="AQ22" s="8"/>
-      <c r="AR22" s="34"/>
-      <c r="AS22" s="35"/>
+      <c r="AR22" s="44"/>
+      <c r="AS22" s="45"/>
       <c r="AT22" s="8"/>
-      <c r="AU22" s="34"/>
-      <c r="AV22" s="35"/>
+      <c r="AU22" s="44"/>
+      <c r="AV22" s="45"/>
       <c r="AW22" s="8"/>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.2">
@@ -5110,12 +5488,12 @@
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="P25" s="8"/>
-      <c r="Q25" s="48" t="s">
+      <c r="Q25" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="R25" s="49"/>
-      <c r="S25" s="49"/>
-      <c r="T25" s="50"/>
+      <c r="R25" s="40"/>
+      <c r="S25" s="40"/>
+      <c r="T25" s="41"/>
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="8"/>
@@ -5125,11 +5503,11 @@
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
-      <c r="AD25" s="36" t="s">
+      <c r="AD25" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="AE25" s="37"/>
-      <c r="AF25" s="38"/>
+      <c r="AE25" s="28"/>
+      <c r="AF25" s="29"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
       <c r="AI25" s="8"/>
@@ -5216,13 +5594,13 @@
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
-      <c r="Q27" s="39">
+      <c r="Q27" s="30">
         <f>SUM(K34:K48)</f>
-        <v>0</v>
-      </c>
-      <c r="R27" s="40"/>
-      <c r="S27" s="40"/>
-      <c r="T27" s="41"/>
+        <v>10</v>
+      </c>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="32"/>
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
       <c r="W27" s="8"/>
@@ -5232,12 +5610,12 @@
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
       <c r="AC27" s="8"/>
-      <c r="AD27" s="39">
+      <c r="AD27" s="30">
         <f>SUM(AD34:AD55)</f>
-        <v>0</v>
-      </c>
-      <c r="AE27" s="40"/>
-      <c r="AF27" s="41"/>
+        <v>3</v>
+      </c>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="32"/>
       <c r="AG27" s="8"/>
       <c r="AH27" s="8"/>
       <c r="AI27" s="8"/>
@@ -5273,10 +5651,10 @@
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="P28" s="8"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="44"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="34"/>
+      <c r="S28" s="34"/>
+      <c r="T28" s="35"/>
       <c r="U28" s="8"/>
       <c r="V28" s="8"/>
       <c r="W28" s="8"/>
@@ -5286,9 +5664,9 @@
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
-      <c r="AD28" s="42"/>
-      <c r="AE28" s="43"/>
-      <c r="AF28" s="44"/>
+      <c r="AD28" s="33"/>
+      <c r="AE28" s="34"/>
+      <c r="AF28" s="35"/>
       <c r="AG28" s="8"/>
       <c r="AH28" s="8"/>
       <c r="AI28" s="8"/>
@@ -5324,10 +5702,10 @@
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
-      <c r="Q29" s="45"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="47"/>
+      <c r="Q29" s="36"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="37"/>
+      <c r="T29" s="38"/>
       <c r="U29" s="8"/>
       <c r="V29" s="8"/>
       <c r="W29" s="8"/>
@@ -5337,9 +5715,9 @@
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
       <c r="AC29" s="8"/>
-      <c r="AD29" s="45"/>
-      <c r="AE29" s="46"/>
-      <c r="AF29" s="47"/>
+      <c r="AD29" s="36"/>
+      <c r="AE29" s="37"/>
+      <c r="AF29" s="38"/>
       <c r="AG29" s="8"/>
       <c r="AH29" s="8"/>
       <c r="AI29" s="8"/>
@@ -5391,7 +5769,7 @@
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
       <c r="AF30" s="8"/>
-      <c r="AG30" s="27" t="s">
+      <c r="AG30" s="26" t="s">
         <v>21</v>
       </c>
       <c r="AH30" s="8"/>
@@ -5412,351 +5790,355 @@
       <c r="AW30" s="8"/>
     </row>
     <row r="34" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J34" s="26">
+      <c r="J34" s="25">
         <v>4</v>
       </c>
-      <c r="K34" s="25">
+      <c r="K34" s="24">
         <f>IF(Respuestas!C6="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC34" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="24">
         <v>15</v>
       </c>
-      <c r="AD34" s="25">
+      <c r="AD34" s="24">
         <f>IF(Respuestas!C17="B",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J35" s="26">
+      <c r="J35" s="25">
         <v>9</v>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="24">
         <f>IF(Respuestas!C11="A",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC35" s="25">
+      <c r="AC35" s="24">
         <v>16</v>
       </c>
-      <c r="AD35" s="25">
+      <c r="AD35" s="24">
         <f>IF(Respuestas!C18="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J36" s="26">
+      <c r="J36" s="25">
         <v>25</v>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="24">
         <f>IF(Respuestas!C27="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC36" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="24">
         <v>18</v>
       </c>
-      <c r="AD36" s="25">
+      <c r="AD36" s="24">
         <f>IF(Respuestas!C20="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J37" s="26">
+      <c r="J37" s="25">
         <v>28</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="24">
         <f>IF(Respuestas!C30="C",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC37" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="24">
         <v>40</v>
       </c>
-      <c r="AD37" s="25">
+      <c r="AD37" s="24">
         <f>IF(Respuestas!C20="A",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J38" s="26">
+      <c r="J38" s="25">
         <v>37</v>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="24">
         <f>IF(Respuestas!C39="C",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC38" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="24">
         <v>42</v>
       </c>
-      <c r="AD38" s="25">
+      <c r="AD38" s="24">
         <f>IF(Respuestas!C44="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J39" s="26">
+      <c r="J39" s="25">
         <v>67</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="24">
         <f>IF(Respuestas!C69="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC39" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="24">
         <v>48</v>
       </c>
-      <c r="AD39" s="25">
+      <c r="AD39" s="24">
         <f>IF(Respuestas!C50="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J40" s="26">
+      <c r="J40" s="25">
         <v>75</v>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="24">
         <f>IF(Respuestas!C77="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC40" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="24">
         <v>58</v>
       </c>
-      <c r="AD40" s="25">
+      <c r="AD40" s="24">
         <f>IF(Respuestas!C60="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J41" s="26">
+      <c r="J41" s="25">
         <v>84</v>
       </c>
-      <c r="K41" s="25">
+      <c r="K41" s="24">
         <f>IF(Respuestas!C86="C",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC41" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="24">
         <v>59</v>
       </c>
-      <c r="AD41" s="25">
+      <c r="AD41" s="24">
         <f>IF(Respuestas!C61="A",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J42" s="26">
+      <c r="J42" s="25">
         <v>92</v>
       </c>
-      <c r="K42" s="25">
+      <c r="K42" s="24">
         <f>IF(Respuestas!C94="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC42" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="24">
         <v>71</v>
       </c>
-      <c r="AD42" s="25">
+      <c r="AD42" s="24">
         <f>IF(Respuestas!C73="A",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J43" s="26">
+      <c r="J43" s="25">
         <v>95</v>
       </c>
-      <c r="K43" s="25">
+      <c r="K43" s="24">
         <f>IF(Respuestas!C97="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC43" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="24">
         <v>77</v>
       </c>
-      <c r="AD43" s="25">
+      <c r="AD43" s="24">
         <f>IF(Respuestas!C79="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J44" s="26">
+      <c r="J44" s="25">
         <v>112</v>
       </c>
-      <c r="K44" s="25">
+      <c r="K44" s="24">
         <f>IF(Respuestas!C114="C",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC44" s="25">
+      <c r="AC44" s="24">
         <v>97</v>
       </c>
-      <c r="AD44" s="25">
+      <c r="AD44" s="24">
         <f>IF(Respuestas!C99="A",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J45" s="26">
+      <c r="J45" s="25">
         <v>113</v>
       </c>
-      <c r="K45" s="25">
+      <c r="K45" s="24">
         <f>IF(Respuestas!C115="C",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC45" s="25">
+      <c r="AC45" s="24">
         <v>102</v>
       </c>
-      <c r="AD45" s="25">
+      <c r="AD45" s="24">
         <f>IF(Respuestas!C104="C",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J46" s="26">
+      <c r="J46" s="25">
         <v>151</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="24">
         <f>IF(Respuestas!C153="C",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC46" s="25">
+      <c r="AC46" s="24">
         <v>105</v>
       </c>
-      <c r="AD46" s="25">
+      <c r="AD46" s="24">
         <f>IF(Respuestas!C107="C",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J47" s="26">
+      <c r="J47" s="25">
         <v>170</v>
       </c>
-      <c r="K47" s="25">
+      <c r="K47" s="24">
         <f>IF(Respuestas!C172="C",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AC47" s="25">
+      <c r="AC47" s="24">
         <v>109</v>
       </c>
-      <c r="AD47" s="25">
+      <c r="AD47" s="24">
         <f>IF(Respuestas!C111="A",1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J48" s="26">
+      <c r="J48" s="25">
         <v>175</v>
       </c>
-      <c r="K48" s="25">
+      <c r="K48" s="24">
         <f>IF(Respuestas!C177="A",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC48" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC48" s="24">
         <v>116</v>
       </c>
-      <c r="AD48" s="25">
+      <c r="AD48" s="24">
         <f>IF(Respuestas!C118="C",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J49" s="26"/>
-      <c r="AC49" s="25">
+      <c r="J49" s="25"/>
+      <c r="AC49" s="24">
         <v>131</v>
       </c>
-      <c r="AD49" s="25">
+      <c r="AD49" s="24">
         <f>IF(Respuestas!C133="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J50" s="26"/>
-      <c r="AC50" s="25">
+      <c r="J50" s="25"/>
+      <c r="AC50" s="24">
         <v>135</v>
       </c>
-      <c r="AD50" s="25">
+      <c r="AD50" s="24">
         <f>IF(Respuestas!C137="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J51" s="26"/>
-      <c r="AC51" s="25">
+      <c r="J51" s="25"/>
+      <c r="AC51" s="24">
         <v>142</v>
       </c>
-      <c r="AD51" s="25">
+      <c r="AD51" s="24">
         <f>IF(Respuestas!C144="C",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J52" s="26"/>
-      <c r="AC52" s="25">
+      <c r="J52" s="25"/>
+      <c r="AC52" s="24">
         <v>153</v>
       </c>
-      <c r="AD52" s="25">
+      <c r="AD52" s="24">
         <f>IF(Respuestas!C155="C",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J53" s="26"/>
-      <c r="AC53" s="25">
+      <c r="J53" s="25"/>
+      <c r="AC53" s="24">
         <v>173</v>
       </c>
-      <c r="AD53" s="25">
+      <c r="AD53" s="24">
         <f>IF(Respuestas!C175="C",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J54" s="26"/>
-      <c r="AC54" s="25">
+      <c r="J54" s="25"/>
+      <c r="AC54" s="24">
         <v>180</v>
       </c>
-      <c r="AD54" s="25">
+      <c r="AD54" s="24">
         <f>IF(Respuestas!C182="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J55" s="26"/>
-      <c r="AC55" s="25">
+      <c r="J55" s="25"/>
+      <c r="AC55" s="24">
         <v>181</v>
       </c>
-      <c r="AD55" s="25">
+      <c r="AD55" s="24">
         <f>IF(Respuestas!C183="B",1,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J56" s="26"/>
+      <c r="J56" s="25"/>
     </row>
     <row r="57" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J57" s="26"/>
+      <c r="J57" s="25"/>
     </row>
     <row r="58" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J58" s="26"/>
+      <c r="J58" s="25"/>
     </row>
     <row r="59" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J59" s="26"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J60" s="26"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J61" s="26"/>
+      <c r="J61" s="25"/>
     </row>
     <row r="62" spans="10:30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="J62" s="26"/>
+      <c r="J62" s="25"/>
     </row>
   </sheetData>
   <sheetProtection password="F5E8" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="36">
-    <mergeCell ref="AD25:AF25"/>
-    <mergeCell ref="AD27:AF29"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="Q27:T29"/>
-    <mergeCell ref="AL21:AM22"/>
-    <mergeCell ref="AO21:AP22"/>
-    <mergeCell ref="AR21:AS22"/>
-    <mergeCell ref="AU21:AV22"/>
-    <mergeCell ref="Z21:AA22"/>
-    <mergeCell ref="AC21:AD22"/>
-    <mergeCell ref="AF21:AG22"/>
-    <mergeCell ref="AI21:AJ22"/>
+    <mergeCell ref="N18:O19"/>
+    <mergeCell ref="Q18:R19"/>
+    <mergeCell ref="T18:U19"/>
+    <mergeCell ref="W18:X19"/>
+    <mergeCell ref="B18:C19"/>
+    <mergeCell ref="E18:F19"/>
+    <mergeCell ref="H18:I19"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="AL18:AM19"/>
+    <mergeCell ref="AO18:AP19"/>
+    <mergeCell ref="AR18:AS19"/>
+    <mergeCell ref="AU18:AV19"/>
+    <mergeCell ref="Z18:AA19"/>
+    <mergeCell ref="AC18:AD19"/>
+    <mergeCell ref="AF18:AG19"/>
+    <mergeCell ref="AI18:AJ19"/>
     <mergeCell ref="N21:O22"/>
     <mergeCell ref="Q21:R22"/>
     <mergeCell ref="T21:U22"/>
@@ -5765,22 +6147,18 @@
     <mergeCell ref="E21:F22"/>
     <mergeCell ref="H21:I22"/>
     <mergeCell ref="K21:L22"/>
-    <mergeCell ref="AL18:AM19"/>
-    <mergeCell ref="AO18:AP19"/>
-    <mergeCell ref="AR18:AS19"/>
-    <mergeCell ref="AU18:AV19"/>
-    <mergeCell ref="Z18:AA19"/>
-    <mergeCell ref="AC18:AD19"/>
-    <mergeCell ref="AF18:AG19"/>
-    <mergeCell ref="AI18:AJ19"/>
-    <mergeCell ref="N18:O19"/>
-    <mergeCell ref="Q18:R19"/>
-    <mergeCell ref="T18:U19"/>
-    <mergeCell ref="W18:X19"/>
-    <mergeCell ref="B18:C19"/>
-    <mergeCell ref="E18:F19"/>
-    <mergeCell ref="H18:I19"/>
-    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="AO21:AP22"/>
+    <mergeCell ref="AR21:AS22"/>
+    <mergeCell ref="AU21:AV22"/>
+    <mergeCell ref="Z21:AA22"/>
+    <mergeCell ref="AC21:AD22"/>
+    <mergeCell ref="AF21:AG22"/>
+    <mergeCell ref="AI21:AJ22"/>
+    <mergeCell ref="AD25:AF25"/>
+    <mergeCell ref="AD27:AF29"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="Q27:T29"/>
+    <mergeCell ref="AL21:AM22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
